--- a/scenarios/Coal_Flexibilisation/sub_scenarios/emissions.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/emissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agatha.majcher\Downloads\agma0 pypsa-rsa master scenarios-Coal_Flexibilisation\sub_scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rlinstitutde-my.sharepoint.com/personal/agatha_majcher_rl-institut_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED405705-344A-4AB9-A060-AD0A7B311041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{ED405705-344A-4AB9-A060-AD0A7B311041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F08A780-7DB6-4F70-BC7E-6FC4B6B6A2AC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7245" yWindow="-15360" windowWidth="17880" windowHeight="13950" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="annual_carbon_constraint" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="48">
   <si>
     <t>scenario</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>ccgt_steam</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -1218,25 +1221,25 @@
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="17">
-        <v>0</v>
-      </c>
-      <c r="D2" s="17">
-        <v>0</v>
-      </c>
-      <c r="E2" s="17">
-        <v>0</v>
-      </c>
-      <c r="F2" s="17">
-        <v>0</v>
-      </c>
-      <c r="G2" s="17">
-        <v>0</v>
-      </c>
-      <c r="H2" s="17">
-        <v>0</v>
-      </c>
-      <c r="I2" s="17">
+      <c r="C2" s="11">
+        <v>190</v>
+      </c>
+      <c r="D2" s="13">
+        <v>236</v>
+      </c>
+      <c r="E2" s="13">
+        <v>308</v>
+      </c>
+      <c r="F2" s="13">
+        <v>347</v>
+      </c>
+      <c r="G2" s="13">
+        <v>385</v>
+      </c>
+      <c r="H2" s="13">
+        <v>424</v>
+      </c>
+      <c r="I2" s="13">
         <v>462</v>
       </c>
       <c r="J2" s="17">
@@ -1390,6 +1393,95 @@
         <v>2188.8000000000002</v>
       </c>
       <c r="AE3" s="18"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
